--- a/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
+++ b/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T21:40:28+00:00</t>
+    <t>2023-12-14T13:07:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
+++ b/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:07:01+00:00</t>
+    <t>2023-12-14T13:50:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
+++ b/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-14T13:50:56+00:00</t>
+    <t>2023-12-15T03:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
+++ b/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T03:05:37+00:00</t>
+    <t>2024-01-19T16:18:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
+++ b/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-19T16:18:21+00:00</t>
+    <t>2024-04-24T00:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
+++ b/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from DIVOC lab test o" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from LabTestSampleOri" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T00:11:34+00:00</t>
+    <t>2024-07-30T07:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>WHO (http://who.int)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -138,7 +138,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://smart.who.int/ddcc/CodeSystem/lab-test-sample-origin-divoc</t>
+    <t>http://smart.who.int/ddcc/CodeSystem/LabTestSampleOriginDivocValueSet</t>
   </si>
 </sst>
 </file>

--- a/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
+++ b/refs/heads/main/ValueSet-lab-test-sample-origin-divoc.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-30T07:55:09+00:00</t>
+    <t>2024-07-30T11:13:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
